--- a/docs/acyl_chain_rule_table_supplement.xlsx
+++ b/docs/acyl_chain_rule_table_supplement.xlsx
@@ -130,7 +130,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -177,7 +177,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -224,7 +224,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -271,7 +271,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -318,7 +318,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular-species notation is parsed using '/' first, then '_', then whitespace if needed.</t>
+          <t xml:space="preserve">Molecular-species notation is parsed using '/' and '_' when present, then whitespace if needed.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">For classes with split='auto', chain parsing tries '/' first, then '_', then whitespace, and otherwise leaves the remaining string unsplit.</t>
+          <t xml:space="preserve">For classes with split='auto', chain parsing splits on '/' and '_' when either delimiter is present, then tries whitespace, and otherwise leaves the remaining string unsplit.</t>
         </is>
       </c>
     </row>
